--- a/dashboard_xbox_subscriptions_eng.xlsx
+++ b/dashboard_xbox_subscriptions_eng.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjetosParaComitarNoGitHub\dashboard_xbox_subscription\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjetosParaComitarNoGitHub\xbox-gamepass-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC540972-19A2-40A7-B712-538304D40940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9481EDF9-2096-4433-B0F6-AC48337E8966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{F158103D-3EF9-4220-8D91-6A4D7428EF98}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="610" activeTab="4" xr2:uid="{F158103D-3EF9-4220-8D91-6A4D7428EF98}"/>
   </bookViews>
   <sheets>
     <sheet name="Assets" sheetId="1" r:id="rId1"/>
@@ -1450,7 +1450,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1502,7 +1502,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
@@ -22155,19 +22154,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B644BE48-7E60-4411-98BE-FD70F0CC6C95}" name="Tabela dinâmica11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="J19:K23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09272748-C2A4-453F-BF6F-69A0C4B8F67D}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="17">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
       <items count="295">
@@ -22468,7 +22460,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
@@ -22476,7 +22468,7 @@
       </items>
     </pivotField>
     <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
@@ -22885,17 +22877,14 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="7"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -22904,14 +22893,793 @@
   <colItems count="1">
     <i/>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
   <dataFields count="1">
     <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
   </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="12" format="5" series="1">
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B05BA7D4-29E8-4A84-A95F-C5299270572E}" name="Tabela dinâmica12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="M5:N8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="17">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="12" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -22923,32 +23691,8 @@
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
+          <reference field="8" count="1" selected="0">
             <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -22966,7 +23710,774 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B47A645-B205-40DB-91BA-7FE9CA530229}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="F12:H15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Soma de Total Value" fld="14" baseField="0" baseItem="0" numFmtId="44"/>
+    <dataField name="Soma de Coupon Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FFB9031-056A-4E4B-ABD0-D96F8F35B9F3}" name="Tabela dinâmica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="F5:G9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
@@ -23735,2329 +25246,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4802289-F633-4CBE-907D-1C284A45E6AE}" name="Tabela dinâmica8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="F26:G32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="17">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="295">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de Total Value" fld="14" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="9" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0000D19F-50B8-4BD2-B52D-03980BE7F157}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B29:C33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="17">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="295">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="7" baseItem="2"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B47A645-B205-40DB-91BA-7FE9CA530229}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="F12:H15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="17">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="295">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Soma de Total Value" fld="14" baseField="0" baseItem="0" numFmtId="44"/>
-    <dataField name="Soma de Coupon Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7C976B7-8B80-462E-BECB-5A39240E67DD}" name="Tabela dinâmica13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="M17:N20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="17">
@@ -26880,7 +26069,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68D78C93-C337-4B36-8BE9-17A828A19406}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
   <location ref="B12:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="17">
@@ -27681,7 +26870,1606 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B644BE48-7E60-4411-98BE-FD70F0CC6C95}" name="Tabela dinâmica11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="J19:K23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="17">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="12" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4802289-F633-4CBE-907D-1C284A45E6AE}" name="Tabela dinâmica8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="F26:G32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Total Value" fld="14" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="9" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45B6DF42-026A-48BE-8E20-3B0D74982B4E}" name="Tabela dinâmica10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="J7:K11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="17">
@@ -28496,13 +29284,20 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B05BA7D4-29E8-4A84-A95F-C5299270572E}" name="Tabela dinâmica12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="M5:N8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0000D19F-50B8-4BD2-B52D-03980BE7F157}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B29:C33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="17">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField numFmtId="164" showAll="0">
       <items count="295">
@@ -28804,805 +29599,6 @@
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="12" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09272748-C2A4-453F-BF6F-69A0C4B8F67D}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="B5:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="17">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="295">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
@@ -30019,14 +30015,17 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="5"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -30039,7 +30038,7 @@
     <pageField fld="7" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
+    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="7" baseItem="2"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -47609,7 +47608,7 @@
       <c r="B6" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6">
         <v>147</v>
       </c>
       <c r="D6">
@@ -47619,13 +47618,13 @@
       <c r="F6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6">
         <v>71</v>
       </c>
       <c r="M6" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="27">
+      <c r="N6">
         <v>197</v>
       </c>
     </row>
@@ -47633,13 +47632,13 @@
       <c r="B7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7">
         <v>148</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7">
         <v>139</v>
       </c>
       <c r="J7" s="16" t="s">
@@ -47651,7 +47650,7 @@
       <c r="M7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="27">
+      <c r="N7">
         <v>98</v>
       </c>
     </row>
@@ -47659,13 +47658,13 @@
       <c r="B8" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8">
         <v>295</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8">
         <v>85</v>
       </c>
       <c r="J8" s="17" t="s">
@@ -47677,7 +47676,7 @@
       <c r="M8" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8">
         <v>295</v>
       </c>
     </row>
@@ -47685,7 +47684,7 @@
       <c r="F9" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9">
         <v>295</v>
       </c>
       <c r="J9" s="17" t="s">
@@ -47889,7 +47888,7 @@
       <c r="M18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="N18" s="27">
+      <c r="N18">
         <v>101</v>
       </c>
     </row>
@@ -47916,7 +47915,7 @@
       <c r="M19" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19">
         <v>194</v>
       </c>
     </row>
@@ -47930,7 +47929,7 @@
       <c r="J20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20">
         <v>71</v>
       </c>
       <c r="L20" s="24">
@@ -47940,7 +47939,7 @@
       <c r="M20" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="N20" s="27">
+      <c r="N20">
         <v>295</v>
       </c>
     </row>
@@ -47954,7 +47953,7 @@
       <c r="J21" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K21">
         <v>139</v>
       </c>
       <c r="L21" s="24">
@@ -47979,7 +47978,7 @@
       <c r="J22" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22">
         <v>85</v>
       </c>
       <c r="L22" s="24">
@@ -48004,7 +48003,7 @@
       <c r="J23" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K23">
         <v>295</v>
       </c>
     </row>
@@ -48106,7 +48105,7 @@
       <c r="B30" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30">
         <v>101</v>
       </c>
       <c r="F30" s="17" t="s">
@@ -48120,7 +48119,7 @@
       <c r="B31" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31">
         <v>96</v>
       </c>
       <c r="F31" s="17" t="s">
@@ -48134,7 +48133,7 @@
       <c r="B32" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32">
         <v>98</v>
       </c>
       <c r="F32" s="17" t="s">
@@ -48148,7 +48147,7 @@
       <c r="B33" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33">
         <v>295</v>
       </c>
     </row>
